--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/137.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/137.xlsx
@@ -426,13 +426,13 @@
         <v>-10.19508603758658</v>
       </c>
       <c r="E2">
-        <v>-12.78723979960071</v>
+        <v>-8.823013653286074</v>
       </c>
       <c r="F2">
-        <v>-5.812590428401623</v>
+        <v>-5.471980662983717</v>
       </c>
       <c r="G2">
-        <v>-14.2207983665533</v>
+        <v>-10.21580331491548</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.28009554748277</v>
       </c>
       <c r="E3">
-        <v>-13.45499951982376</v>
+        <v>-8.99608287291122</v>
       </c>
       <c r="F3">
-        <v>-5.79335325220641</v>
+        <v>-5.378928495892443</v>
       </c>
       <c r="G3">
-        <v>-13.54840880398111</v>
+        <v>-10.35993097191409</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.37961787145075</v>
       </c>
       <c r="E4">
-        <v>-14.04323017952411</v>
+        <v>-9.567743846217503</v>
       </c>
       <c r="F4">
-        <v>-5.424324686300661</v>
+        <v>-5.625521046194813</v>
       </c>
       <c r="G4">
-        <v>-14.34763562654441</v>
+        <v>-9.744583805542071</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.46428432018214</v>
       </c>
       <c r="E5">
-        <v>-14.29375441857645</v>
+        <v>-10.78669130875816</v>
       </c>
       <c r="F5">
-        <v>-5.670655472503747</v>
+        <v>-5.71782519752136</v>
       </c>
       <c r="G5">
-        <v>-14.24553385527917</v>
+        <v>-10.02729385510383</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.52195555971367</v>
       </c>
       <c r="E6">
-        <v>-15.68066751053561</v>
+        <v>-11.48769455667153</v>
       </c>
       <c r="F6">
-        <v>-5.343959794350664</v>
+        <v>-5.803364072269242</v>
       </c>
       <c r="G6">
-        <v>-14.67426810790089</v>
+        <v>-10.95452113070107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.54288239489716</v>
       </c>
       <c r="E7">
-        <v>-16.06964078542446</v>
+        <v>-12.08549388195008</v>
       </c>
       <c r="F7">
-        <v>-5.232304980494722</v>
+        <v>-5.610213644958481</v>
       </c>
       <c r="G7">
-        <v>-14.12521966374823</v>
+        <v>-10.27932448308478</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.50876536609911</v>
       </c>
       <c r="E8">
-        <v>-16.49750912356518</v>
+        <v>-11.82948566087446</v>
       </c>
       <c r="F8">
-        <v>-5.276969722486268</v>
+        <v>-5.492211051694886</v>
       </c>
       <c r="G8">
-        <v>-13.96557018816267</v>
+        <v>-10.00427936708588</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.41951322220642</v>
       </c>
       <c r="E9">
-        <v>-16.79328187490216</v>
+        <v>-13.01121359554607</v>
       </c>
       <c r="F9">
-        <v>-5.529503323801517</v>
+        <v>-5.490864126297934</v>
       </c>
       <c r="G9">
-        <v>-13.67723284362646</v>
+        <v>-9.559358848511417</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.26744669392004</v>
       </c>
       <c r="E10">
-        <v>-17.50083782470463</v>
+        <v>-13.28014155296558</v>
       </c>
       <c r="F10">
-        <v>-5.313026070427923</v>
+        <v>-5.251336721574041</v>
       </c>
       <c r="G10">
-        <v>-13.57721792927303</v>
+        <v>-9.929825168680521</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.06091552007944</v>
       </c>
       <c r="E11">
-        <v>-18.14260410412366</v>
+        <v>-13.77571057752098</v>
       </c>
       <c r="F11">
-        <v>-5.582420261859752</v>
+        <v>-5.801506044184763</v>
       </c>
       <c r="G11">
-        <v>-13.20627255075625</v>
+        <v>-10.21783110983922</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.819668300198844</v>
       </c>
       <c r="E12">
-        <v>-19.26276743466099</v>
+        <v>-15.74225022856592</v>
       </c>
       <c r="F12">
-        <v>-5.33964731365169</v>
+        <v>-5.73514138970948</v>
       </c>
       <c r="G12">
-        <v>-13.10669403887022</v>
+        <v>-8.891919008661647</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.56187323394831</v>
       </c>
       <c r="E13">
-        <v>-19.28688608722585</v>
+        <v>-16.16467081247542</v>
       </c>
       <c r="F13">
-        <v>-5.254628653632766</v>
+        <v>-5.400505810000564</v>
       </c>
       <c r="G13">
-        <v>-12.48805908849563</v>
+        <v>-8.486596271866562</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.329648631369766</v>
       </c>
       <c r="E14">
-        <v>-20.617709500126</v>
+        <v>-17.11085922858608</v>
       </c>
       <c r="F14">
-        <v>-5.030643078120196</v>
+        <v>-5.267724313903623</v>
       </c>
       <c r="G14">
-        <v>-12.60983834545286</v>
+        <v>-7.24385985599935</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.147516822142327</v>
       </c>
       <c r="E15">
-        <v>-20.79676536238929</v>
+        <v>-18.85192615878911</v>
       </c>
       <c r="F15">
-        <v>-5.049969717994911</v>
+        <v>-5.128923071890538</v>
       </c>
       <c r="G15">
-        <v>-12.39923642088146</v>
+        <v>-7.385100038025648</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.042898732164858</v>
       </c>
       <c r="E16">
-        <v>-20.79460528028763</v>
+        <v>-18.2803104702229</v>
       </c>
       <c r="F16">
-        <v>-4.63507941920057</v>
+        <v>-4.935365916185003</v>
       </c>
       <c r="G16">
-        <v>-11.91925933116589</v>
+        <v>-6.993568275444908</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.027205978327446</v>
       </c>
       <c r="E17">
-        <v>-21.43710970096991</v>
+        <v>-20.00313217864903</v>
       </c>
       <c r="F17">
-        <v>-4.664839346513546</v>
+        <v>-4.177891024084482</v>
       </c>
       <c r="G17">
-        <v>-10.98940379709953</v>
+        <v>-7.673745817388441</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.090284857134927</v>
       </c>
       <c r="E18">
-        <v>-22.96184689935252</v>
+        <v>-19.63470006185898</v>
       </c>
       <c r="F18">
-        <v>-4.379345006240905</v>
+        <v>-3.922940246687864</v>
       </c>
       <c r="G18">
-        <v>-10.75111820623109</v>
+        <v>-6.580242639266335</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.225358375273563</v>
       </c>
       <c r="E19">
-        <v>-23.52372184032822</v>
+        <v>-19.55828206297954</v>
       </c>
       <c r="F19">
-        <v>-4.019734977704986</v>
+        <v>-4.179129433351667</v>
       </c>
       <c r="G19">
-        <v>-11.00046151375486</v>
+        <v>-6.999599160671167</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.400434828049953</v>
       </c>
       <c r="E20">
-        <v>-24.46556744986553</v>
+        <v>-20.61907257080231</v>
       </c>
       <c r="F20">
-        <v>-3.926797953682701</v>
+        <v>-3.869277777967109</v>
       </c>
       <c r="G20">
-        <v>-10.14938810933076</v>
+        <v>-7.384893321067403</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.592147938208457</v>
       </c>
       <c r="E21">
-        <v>-24.65888800525298</v>
+        <v>-21.96451389779923</v>
       </c>
       <c r="F21">
-        <v>-3.802142741807223</v>
+        <v>-3.87626422864232</v>
       </c>
       <c r="G21">
-        <v>-10.3018467878688</v>
+        <v>-6.863615495583099</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.771037063332578</v>
       </c>
       <c r="E22">
-        <v>-25.94217602649462</v>
+        <v>-22.71975015042845</v>
       </c>
       <c r="F22">
-        <v>-3.725860872785625</v>
+        <v>-3.295710389696912</v>
       </c>
       <c r="G22">
-        <v>-10.66385740007922</v>
+        <v>-7.136741096969718</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.905961784811767</v>
       </c>
       <c r="E23">
-        <v>-25.77864377312963</v>
+        <v>-22.44071463902382</v>
       </c>
       <c r="F23">
-        <v>-3.769288862244792</v>
+        <v>-3.170547388603517</v>
       </c>
       <c r="G23">
-        <v>-9.935258871582963</v>
+        <v>-7.268810264737368</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.982973032757283</v>
       </c>
       <c r="E24">
-        <v>-26.15058545727562</v>
+        <v>-23.01789129367145</v>
       </c>
       <c r="F24">
-        <v>-3.502609230791936</v>
+        <v>-2.597015620131641</v>
       </c>
       <c r="G24">
-        <v>-10.8030927557327</v>
+        <v>-7.510797073524857</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.97990086963898</v>
       </c>
       <c r="E25">
-        <v>-26.87989619621093</v>
+        <v>-24.62258322913348</v>
       </c>
       <c r="F25">
-        <v>-3.526384203619684</v>
+        <v>-2.918260640774303</v>
       </c>
       <c r="G25">
-        <v>-10.18653481860524</v>
+        <v>-7.394054491661373</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.895239936365154</v>
       </c>
       <c r="E26">
-        <v>-26.66344419559231</v>
+        <v>-22.90883205414472</v>
       </c>
       <c r="F26">
-        <v>-3.47041390331473</v>
+        <v>-3.147966093203203</v>
       </c>
       <c r="G26">
-        <v>-10.55741129146928</v>
+        <v>-7.574154180616175</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.729016033065392</v>
       </c>
       <c r="E27">
-        <v>-26.34624270525103</v>
+        <v>-23.9767096237895</v>
       </c>
       <c r="F27">
-        <v>-3.172038449928557</v>
+        <v>-3.098499305377628</v>
       </c>
       <c r="G27">
-        <v>-9.895572496821478</v>
+        <v>-7.89622904522659</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.486419875581419</v>
       </c>
       <c r="E28">
-        <v>-26.87871879296894</v>
+        <v>-23.07637653548051</v>
       </c>
       <c r="F28">
-        <v>-3.209443380001968</v>
+        <v>-3.361633524346502</v>
       </c>
       <c r="G28">
-        <v>-10.07960308920449</v>
+        <v>-7.458704400047112</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.186573234986684</v>
       </c>
       <c r="E29">
-        <v>-26.09147075757949</v>
+        <v>-23.2773411549929</v>
       </c>
       <c r="F29">
-        <v>-3.50938941798385</v>
+        <v>-3.33291899669586</v>
       </c>
       <c r="G29">
-        <v>-10.9657888455362</v>
+        <v>-7.211848258465408</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.839361148377446</v>
       </c>
       <c r="E30">
-        <v>-26.01670565171286</v>
+        <v>-22.94763201944244</v>
       </c>
       <c r="F30">
-        <v>-3.389753284201934</v>
+        <v>-3.092381812107953</v>
       </c>
       <c r="G30">
-        <v>-10.4422863518346</v>
+        <v>-7.00743799897668</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.47020257707144</v>
       </c>
       <c r="E31">
-        <v>-25.99050390110447</v>
+        <v>-21.86104732367198</v>
       </c>
       <c r="F31">
-        <v>-3.528745050717663</v>
+        <v>-3.061706538814885</v>
       </c>
       <c r="G31">
-        <v>-10.68046038117001</v>
+        <v>-7.099262984317741</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.097567127765918</v>
       </c>
       <c r="E32">
-        <v>-25.39464729117521</v>
+        <v>-23.52263953504039</v>
       </c>
       <c r="F32">
-        <v>-3.506318660021672</v>
+        <v>-3.097043035483506</v>
       </c>
       <c r="G32">
-        <v>-10.1448304925847</v>
+        <v>-7.036545715430514</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.739683536534254</v>
       </c>
       <c r="E33">
-        <v>-26.03579769812919</v>
+        <v>-22.66715192482936</v>
       </c>
       <c r="F33">
-        <v>-3.818237920443617</v>
+        <v>-3.017626624209715</v>
       </c>
       <c r="G33">
-        <v>-10.34679296079008</v>
+        <v>-6.912384291621127</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.421853968615672</v>
       </c>
       <c r="E34">
-        <v>-25.04733597715693</v>
+        <v>-23.31469200860817</v>
       </c>
       <c r="F34">
-        <v>-3.415593376964862</v>
+        <v>-3.146464263101927</v>
       </c>
       <c r="G34">
-        <v>-10.12666565003161</v>
+        <v>-5.502089015599312</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.153944066394277</v>
       </c>
       <c r="E35">
-        <v>-25.29399742788073</v>
+        <v>-22.46173128689342</v>
       </c>
       <c r="F35">
-        <v>-3.175838171205198</v>
+        <v>-3.33383351430855</v>
       </c>
       <c r="G35">
-        <v>-9.596764774289086</v>
+        <v>-6.281208512446341</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.958256733104287</v>
       </c>
       <c r="E36">
-        <v>-24.62688980791478</v>
+        <v>-21.95120471269069</v>
       </c>
       <c r="F36">
-        <v>-3.782921304592663</v>
+        <v>-3.443570657627012</v>
       </c>
       <c r="G36">
-        <v>-9.469450096561072</v>
+        <v>-7.042615975315488</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.841545633608547</v>
       </c>
       <c r="E37">
-        <v>-24.71858687809609</v>
+        <v>-22.7851322581512</v>
       </c>
       <c r="F37">
-        <v>-3.892046284400456</v>
+        <v>-3.078378261163628</v>
       </c>
       <c r="G37">
-        <v>-9.55620559459279</v>
+        <v>-5.468335089417304</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.810329412829275</v>
       </c>
       <c r="E38">
-        <v>-24.22570323862725</v>
+        <v>-21.93225304896859</v>
       </c>
       <c r="F38">
-        <v>-3.502291137709261</v>
+        <v>-3.225252771884397</v>
       </c>
       <c r="G38">
-        <v>-9.956324313994598</v>
+        <v>-5.049077004659256</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.870707139570768</v>
       </c>
       <c r="E39">
-        <v>-23.26315797440088</v>
+        <v>-21.22785344554947</v>
       </c>
       <c r="F39">
-        <v>-3.719152753557755</v>
+        <v>-3.36879973074812</v>
       </c>
       <c r="G39">
-        <v>-9.657720027198891</v>
+        <v>-5.484016047249891</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.010647664848142</v>
       </c>
       <c r="E40">
-        <v>-23.53619778621936</v>
+        <v>-21.5240065887031</v>
       </c>
       <c r="F40">
-        <v>-3.629588013232266</v>
+        <v>-3.602427502829276</v>
       </c>
       <c r="G40">
-        <v>-9.346118821806224</v>
+        <v>-5.073613979480784</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.227376636567437</v>
       </c>
       <c r="E41">
-        <v>-23.66860583772963</v>
+        <v>-19.76220830449295</v>
       </c>
       <c r="F41">
-        <v>-3.60082792537447</v>
+        <v>-3.693082374656849</v>
       </c>
       <c r="G41">
-        <v>-9.45882550115159</v>
+        <v>-4.386831338538088</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.498214920259779</v>
       </c>
       <c r="E42">
-        <v>-22.35712806579024</v>
+        <v>-19.87595451461761</v>
       </c>
       <c r="F42">
-        <v>-3.805177051603677</v>
+        <v>-3.786802205874779</v>
       </c>
       <c r="G42">
-        <v>-9.053368234272565</v>
+        <v>-5.285452924580094</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.805803723558189</v>
       </c>
       <c r="E43">
-        <v>-21.98901294218073</v>
+        <v>-19.46096968502871</v>
       </c>
       <c r="F43">
-        <v>-3.68661448197579</v>
+        <v>-3.432708275874102</v>
       </c>
       <c r="G43">
-        <v>-8.641883363388841</v>
+        <v>-5.527023018229532</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.1330913290771</v>
       </c>
       <c r="E44">
-        <v>-22.71920673354753</v>
+        <v>-18.51212758314956</v>
       </c>
       <c r="F44">
-        <v>-3.816600238088283</v>
+        <v>-3.830633610259109</v>
       </c>
       <c r="G44">
-        <v>-9.150334893797275</v>
+        <v>-5.041402227431714</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.45658765326837</v>
       </c>
       <c r="E45">
-        <v>-21.45936715071761</v>
+        <v>-19.76499784448167</v>
       </c>
       <c r="F45">
-        <v>-3.889764132205744</v>
+        <v>-3.718043569605406</v>
       </c>
       <c r="G45">
-        <v>-9.52807896338523</v>
+        <v>-5.712389067787242</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.769242287925413</v>
       </c>
       <c r="E46">
-        <v>-21.36461336058111</v>
+        <v>-16.894733278096</v>
       </c>
       <c r="F46">
-        <v>-4.009585820285887</v>
+        <v>-3.500217734100054</v>
       </c>
       <c r="G46">
-        <v>-9.191159852439887</v>
+        <v>-5.205194245236076</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.05161118753313</v>
       </c>
       <c r="E47">
-        <v>-21.52665121752358</v>
+        <v>-17.73445274181233</v>
       </c>
       <c r="F47">
-        <v>-3.820307182215811</v>
+        <v>-4.099485221042105</v>
       </c>
       <c r="G47">
-        <v>-9.039971006645352</v>
+        <v>-5.457953304403222</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.298485467922507</v>
       </c>
       <c r="E48">
-        <v>-20.47962274221011</v>
+        <v>-17.56036008706145</v>
       </c>
       <c r="F48">
-        <v>-4.108471350627674</v>
+        <v>-3.949546579298381</v>
       </c>
       <c r="G48">
-        <v>-9.70564226807458</v>
+        <v>-5.016816034286795</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.505558183387446</v>
       </c>
       <c r="E49">
-        <v>-20.43086919104353</v>
+        <v>-16.53383201358071</v>
       </c>
       <c r="F49">
-        <v>-4.087812695969258</v>
+        <v>-4.213995417335498</v>
       </c>
       <c r="G49">
-        <v>-9.485583862968861</v>
+        <v>-4.99421169896378</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.669477978024052</v>
       </c>
       <c r="E50">
-        <v>-19.77402309317896</v>
+        <v>-16.97572503572319</v>
       </c>
       <c r="F50">
-        <v>-3.758597124176859</v>
+        <v>-4.085015299250004</v>
       </c>
       <c r="G50">
-        <v>-9.841635776827326</v>
+        <v>-4.589233490432435</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.804153054000961</v>
       </c>
       <c r="E51">
-        <v>-20.04529680013445</v>
+        <v>-17.20307254480427</v>
       </c>
       <c r="F51">
-        <v>-3.893732012065153</v>
+        <v>-4.248018951670682</v>
       </c>
       <c r="G51">
-        <v>-9.06179113001566</v>
+        <v>-5.293124420586075</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.910921563264719</v>
       </c>
       <c r="E52">
-        <v>-19.06641280168841</v>
+        <v>-17.46605914432572</v>
       </c>
       <c r="F52">
-        <v>-4.178798086390547</v>
+        <v>-4.264176257862286</v>
       </c>
       <c r="G52">
-        <v>-9.422784563542649</v>
+        <v>-5.087660888976766</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.0061226719609</v>
       </c>
       <c r="E53">
-        <v>-17.69563013414457</v>
+        <v>-16.87744356433472</v>
       </c>
       <c r="F53">
-        <v>-4.116175995841113</v>
+        <v>-4.141574568778348</v>
       </c>
       <c r="G53">
-        <v>-9.446452014650923</v>
+        <v>-4.683506267056842</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.09878525234419</v>
       </c>
       <c r="E54">
-        <v>-18.43474049083248</v>
+        <v>-15.51095389015015</v>
       </c>
       <c r="F54">
-        <v>-4.244463598777867</v>
+        <v>-4.095744313851063</v>
       </c>
       <c r="G54">
-        <v>-9.295338636952257</v>
+        <v>-5.434243197414673</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.19298659813892</v>
       </c>
       <c r="E55">
-        <v>-17.60992876354941</v>
+        <v>-15.72801723475981</v>
       </c>
       <c r="F55">
-        <v>-4.269610348024651</v>
+        <v>-4.064470130925771</v>
       </c>
       <c r="G55">
-        <v>-9.948734848527602</v>
+        <v>-5.736981823375281</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.30149133656968</v>
       </c>
       <c r="E56">
-        <v>-17.39019361927522</v>
+        <v>-14.62860790059963</v>
       </c>
       <c r="F56">
-        <v>-4.243090165624025</v>
+        <v>-4.255298644406484</v>
       </c>
       <c r="G56">
-        <v>-9.303961687210478</v>
+        <v>-5.278106269508497</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.41752582889462</v>
       </c>
       <c r="E57">
-        <v>-17.22255403998527</v>
+        <v>-14.2745355748879</v>
       </c>
       <c r="F57">
-        <v>-3.919983803427272</v>
+        <v>-4.049617503393575</v>
       </c>
       <c r="G57">
-        <v>-9.690446931032792</v>
+        <v>-6.341084243463088</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.54825781186074</v>
       </c>
       <c r="E58">
-        <v>-16.85438004621365</v>
+        <v>-12.38789179076029</v>
       </c>
       <c r="F58">
-        <v>-4.1493421699144</v>
+        <v>-3.92863527258211</v>
       </c>
       <c r="G58">
-        <v>-9.804649847409266</v>
+        <v>-5.301360286700281</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.68823602730203</v>
       </c>
       <c r="E59">
-        <v>-17.75087298856414</v>
+        <v>-14.25103732326209</v>
       </c>
       <c r="F59">
-        <v>-4.133739869882671</v>
+        <v>-3.75104324183073</v>
       </c>
       <c r="G59">
-        <v>-10.07369689039749</v>
+        <v>-6.17343022788326</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.82961535720376</v>
       </c>
       <c r="E60">
-        <v>-16.63556871063703</v>
+        <v>-13.78494866449663</v>
       </c>
       <c r="F60">
-        <v>-3.981487597982927</v>
+        <v>-3.665985648543874</v>
       </c>
       <c r="G60">
-        <v>-10.13027827496856</v>
+        <v>-6.020161087620038</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.97409955941922</v>
       </c>
       <c r="E61">
-        <v>-16.06984003828079</v>
+        <v>-12.65702352951014</v>
       </c>
       <c r="F61">
-        <v>-4.180777884483238</v>
+        <v>-4.217337879805794</v>
       </c>
       <c r="G61">
-        <v>-10.30421911105628</v>
+        <v>-6.233256740576616</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.10618297220043</v>
       </c>
       <c r="E62">
-        <v>-15.83745686610318</v>
+        <v>-13.78036132032686</v>
       </c>
       <c r="F62">
-        <v>-3.951508981675613</v>
+        <v>-3.968774643452163</v>
       </c>
       <c r="G62">
-        <v>-10.85817134082954</v>
+        <v>-6.534597566152899</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.2310408344989</v>
       </c>
       <c r="E63">
-        <v>-15.29677518348337</v>
+        <v>-13.28135518399964</v>
       </c>
       <c r="F63">
-        <v>-4.375152638815337</v>
+        <v>-3.834565041952795</v>
       </c>
       <c r="G63">
-        <v>-10.73541756106915</v>
+        <v>-6.587359608828771</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.34275660766251</v>
       </c>
       <c r="E64">
-        <v>-15.49394947025135</v>
+        <v>-12.6175035368452</v>
       </c>
       <c r="F64">
-        <v>-3.78417793794271</v>
+        <v>-3.454544040611897</v>
       </c>
       <c r="G64">
-        <v>-11.57805494486391</v>
+        <v>-6.700827531575928</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.43918483620881</v>
       </c>
       <c r="E65">
-        <v>-16.05412170500017</v>
+        <v>-13.89304786753373</v>
       </c>
       <c r="F65">
-        <v>-3.83062201311547</v>
+        <v>-3.9892618260582</v>
       </c>
       <c r="G65">
-        <v>-11.02103149171102</v>
+        <v>-7.595137592488824</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.52714218177702</v>
       </c>
       <c r="E66">
-        <v>-14.39457636388322</v>
+        <v>-13.36144124682529</v>
       </c>
       <c r="F66">
-        <v>-4.252676033209221</v>
+        <v>-3.675740503079241</v>
       </c>
       <c r="G66">
-        <v>-11.34093418764908</v>
+        <v>-7.801132681990762</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.59947089280793</v>
       </c>
       <c r="E67">
-        <v>-15.3174567242764</v>
+        <v>-13.03713458076598</v>
       </c>
       <c r="F67">
-        <v>-4.236723333766108</v>
+        <v>-3.456443487066517</v>
       </c>
       <c r="G67">
-        <v>-11.11179008004526</v>
+        <v>-7.788037326747019</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.66900764288994</v>
       </c>
       <c r="E68">
-        <v>-15.93841466563018</v>
+        <v>-11.32783036725275</v>
       </c>
       <c r="F68">
-        <v>-3.934437986238721</v>
+        <v>-4.024236326171798</v>
       </c>
       <c r="G68">
-        <v>-11.47361694384835</v>
+        <v>-8.026657602214517</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.73357044301</v>
       </c>
       <c r="E69">
-        <v>-15.27694499580378</v>
+        <v>-12.2321575696365</v>
       </c>
       <c r="F69">
-        <v>-4.183813022647096</v>
+        <v>-3.937863285449297</v>
       </c>
       <c r="G69">
-        <v>-11.52916802484974</v>
+        <v>-7.552347182132105</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.7953695982147</v>
       </c>
       <c r="E70">
-        <v>-14.57634025360309</v>
+        <v>-12.35664532010736</v>
       </c>
       <c r="F70">
-        <v>-4.158579294823016</v>
+        <v>-4.303468208879275</v>
       </c>
       <c r="G70">
-        <v>-11.23864866797651</v>
+        <v>-7.822178437073041</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.86013836586088</v>
       </c>
       <c r="E71">
-        <v>-15.30807372613251</v>
+        <v>-12.6572318393145</v>
       </c>
       <c r="F71">
-        <v>-4.156394061614431</v>
+        <v>-3.731609742561053</v>
       </c>
       <c r="G71">
-        <v>-11.25034950405749</v>
+        <v>-8.566884482204614</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.91756041675291</v>
       </c>
       <c r="E72">
-        <v>-15.88824823057321</v>
+        <v>-12.56118290561181</v>
       </c>
       <c r="F72">
-        <v>-4.367923476491105</v>
+        <v>-4.023914919619513</v>
       </c>
       <c r="G72">
-        <v>-11.46857370631148</v>
+        <v>-8.085489904775361</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.97516952751971</v>
       </c>
       <c r="E73">
-        <v>-15.94310616470213</v>
+        <v>-12.3349992143507</v>
       </c>
       <c r="F73">
-        <v>-4.116981168956634</v>
+        <v>-3.938399239158908</v>
       </c>
       <c r="G73">
-        <v>-11.16300338614507</v>
+        <v>-8.145444385109535</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.02243639735171</v>
       </c>
       <c r="E74">
-        <v>-15.70266230879086</v>
+        <v>-11.53902933802248</v>
       </c>
       <c r="F74">
-        <v>-4.212354421510552</v>
+        <v>-3.764170380062894</v>
       </c>
       <c r="G74">
-        <v>-11.44632046169532</v>
+        <v>-8.410872240717696</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.0565686217699</v>
       </c>
       <c r="E75">
-        <v>-16.13398134412544</v>
+        <v>-12.46995226825328</v>
       </c>
       <c r="F75">
-        <v>-4.412408462756244</v>
+        <v>-4.164063915396953</v>
       </c>
       <c r="G75">
-        <v>-11.3618224440965</v>
+        <v>-7.711919549011021</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.07735061321909</v>
       </c>
       <c r="E76">
-        <v>-16.42902953962119</v>
+        <v>-12.66539214947632</v>
       </c>
       <c r="F76">
-        <v>-4.521104348249387</v>
+        <v>-4.361435702992379</v>
       </c>
       <c r="G76">
-        <v>-10.50096115576059</v>
+        <v>-7.372076869656212</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.07358164788022</v>
       </c>
       <c r="E77">
-        <v>-16.25413081649695</v>
+        <v>-13.48189865542932</v>
       </c>
       <c r="F77">
-        <v>-4.180399320580158</v>
+        <v>-3.953051401779626</v>
       </c>
       <c r="G77">
-        <v>-10.66632815991348</v>
+        <v>-6.566668225674912</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.05393707322827</v>
       </c>
       <c r="E78">
-        <v>-17.0217207462191</v>
+        <v>-15.20554001765084</v>
       </c>
       <c r="F78">
-        <v>-4.39994981701814</v>
+        <v>-4.239992071537555</v>
       </c>
       <c r="G78">
-        <v>-10.6808574089787</v>
+        <v>-6.336270691435383</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.01078682434741</v>
       </c>
       <c r="E79">
-        <v>-17.18821915005911</v>
+        <v>-14.36211626219624</v>
       </c>
       <c r="F79">
-        <v>-4.477971257585616</v>
+        <v>-4.570460134842987</v>
       </c>
       <c r="G79">
-        <v>-10.39077117335132</v>
+        <v>-7.124758075834627</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.94978913312165</v>
       </c>
       <c r="E80">
-        <v>-17.75820458798255</v>
+        <v>-14.44679872613968</v>
       </c>
       <c r="F80">
-        <v>-4.799464788449119</v>
+        <v>-4.181791806184265</v>
       </c>
       <c r="G80">
-        <v>-10.27055377785638</v>
+        <v>-7.049828100303147</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.87587611825396</v>
       </c>
       <c r="E81">
-        <v>-18.4943261518254</v>
+        <v>-14.01394906659051</v>
       </c>
       <c r="F81">
-        <v>-4.410238140160909</v>
+        <v>-5.200979438790456</v>
       </c>
       <c r="G81">
-        <v>-10.20926055912595</v>
+        <v>-7.117716574368058</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.78425521174047</v>
       </c>
       <c r="E82">
-        <v>-18.94340133374405</v>
+        <v>-16.68805825285994</v>
       </c>
       <c r="F82">
-        <v>-4.68309159386683</v>
+        <v>-4.75184360319698</v>
       </c>
       <c r="G82">
-        <v>-10.63157346115584</v>
+        <v>-6.824280211528476</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.69026410744271</v>
       </c>
       <c r="E83">
-        <v>-19.20447238876025</v>
+        <v>-16.5449856450616</v>
       </c>
       <c r="F83">
-        <v>-4.879265562197808</v>
+        <v>-4.829018452278796</v>
       </c>
       <c r="G83">
-        <v>-10.13525588807424</v>
+        <v>-6.773792055393301</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.5900520140244</v>
       </c>
       <c r="E84">
-        <v>-20.56742079627082</v>
+        <v>-17.64809021401204</v>
       </c>
       <c r="F84">
-        <v>-5.009684554461966</v>
+        <v>-4.869939801977092</v>
       </c>
       <c r="G84">
-        <v>-9.327678356642144</v>
+        <v>-6.411998003805807</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.49409647862547</v>
       </c>
       <c r="E85">
-        <v>-21.76248961536904</v>
+        <v>-18.31709526458721</v>
       </c>
       <c r="F85">
-        <v>-5.166146589502737</v>
+        <v>-5.042074548278829</v>
       </c>
       <c r="G85">
-        <v>-9.86206138103487</v>
+        <v>-5.955488210683383</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.40851555511067</v>
       </c>
       <c r="E86">
-        <v>-22.22324826022748</v>
+        <v>-19.7869745288409</v>
       </c>
       <c r="F86">
-        <v>-5.259342064154695</v>
+        <v>-5.333495028951099</v>
       </c>
       <c r="G86">
-        <v>-9.986406553251587</v>
+        <v>-6.678341320229054</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.33187076602705</v>
       </c>
       <c r="E87">
-        <v>-24.0505101646925</v>
+        <v>-21.47609986217595</v>
       </c>
       <c r="F87">
-        <v>-5.329164324169263</v>
+        <v>-5.017871309503834</v>
       </c>
       <c r="G87">
-        <v>-10.04205278967821</v>
+        <v>-6.496847112111488</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.27988812416482</v>
       </c>
       <c r="E88">
-        <v>-24.83715591303893</v>
+        <v>-21.38557113828861</v>
       </c>
       <c r="F88">
-        <v>-5.449341381865207</v>
+        <v>-5.724427285721672</v>
       </c>
       <c r="G88">
-        <v>-9.63845925664495</v>
+        <v>-6.900142053982838</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.24655029379919</v>
       </c>
       <c r="E89">
-        <v>-26.91011923173813</v>
+        <v>-23.82729715238042</v>
       </c>
       <c r="F89">
-        <v>-5.704519960297594</v>
+        <v>-5.940903710727864</v>
       </c>
       <c r="G89">
-        <v>-9.983742201345317</v>
+        <v>-6.779672004427826</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.24355816404889</v>
       </c>
       <c r="E90">
-        <v>-27.89819603241974</v>
+        <v>-25.53470393528444</v>
       </c>
       <c r="F90">
-        <v>-5.71591084045349</v>
+        <v>-5.495388669052025</v>
       </c>
       <c r="G90">
-        <v>-9.774597139146312</v>
+        <v>-6.853220585682779</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.27255795241534</v>
       </c>
       <c r="E91">
-        <v>-28.70389307091643</v>
+        <v>-27.19422663403135</v>
       </c>
       <c r="F91">
-        <v>-5.490237052174015</v>
+        <v>-5.804233858042181</v>
       </c>
       <c r="G91">
-        <v>-10.1772981799154</v>
+        <v>-7.415454618672071</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.33069334601201</v>
       </c>
       <c r="E92">
-        <v>-31.22507568994683</v>
+        <v>-29.48984596273968</v>
       </c>
       <c r="F92">
-        <v>-5.654392135284585</v>
+        <v>-6.001248619287002</v>
       </c>
       <c r="G92">
-        <v>-10.35480570383824</v>
+        <v>-7.839473755912874</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.42776437779937</v>
       </c>
       <c r="E93">
-        <v>-32.74022384461819</v>
+        <v>-31.65149265216809</v>
       </c>
       <c r="F93">
-        <v>-5.633485798772731</v>
+        <v>-6.476136740698708</v>
       </c>
       <c r="G93">
-        <v>-10.69005795423139</v>
+        <v>-7.322671516635653</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.5508325294605</v>
       </c>
       <c r="E94">
-        <v>-34.97177432306601</v>
+        <v>-33.32696463637002</v>
       </c>
       <c r="F94">
-        <v>-5.570841342303421</v>
+        <v>-6.049240084768192</v>
       </c>
       <c r="G94">
-        <v>-10.54580232959196</v>
+        <v>-7.847388062314255</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.70677722917362</v>
       </c>
       <c r="E95">
-        <v>-36.7568580206236</v>
+        <v>-36.36273360655102</v>
       </c>
       <c r="F95">
-        <v>-5.743171583312219</v>
+        <v>-6.439976846831704</v>
       </c>
       <c r="G95">
-        <v>-10.73293695757021</v>
+        <v>-8.17477850585097</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.88932635098806</v>
       </c>
       <c r="E96">
-        <v>-38.6709511499487</v>
+        <v>-39.20960860468708</v>
       </c>
       <c r="F96">
-        <v>-5.673297136151275</v>
+        <v>-6.222536202168653</v>
       </c>
       <c r="G96">
-        <v>-10.45016456479882</v>
+        <v>-8.869623108165221</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.08842321857441</v>
       </c>
       <c r="E97">
-        <v>-41.3915745569879</v>
+        <v>-40.0298465732224</v>
       </c>
       <c r="F97">
-        <v>-5.723471349738841</v>
+        <v>-6.122482673788918</v>
       </c>
       <c r="G97">
-        <v>-11.15580766726521</v>
+        <v>-8.087665354669273</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.31285880577558</v>
       </c>
       <c r="E98">
-        <v>-43.68507003138664</v>
+        <v>-43.22042142735562</v>
       </c>
       <c r="F98">
-        <v>-5.633274565085017</v>
+        <v>-6.031600000925576</v>
       </c>
       <c r="G98">
-        <v>-11.47746253551601</v>
+        <v>-8.826356920682382</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.53987115662948</v>
       </c>
       <c r="E99">
-        <v>-46.07989916865502</v>
+        <v>-45.19650936584573</v>
       </c>
       <c r="F99">
-        <v>-5.733887241461642</v>
+        <v>-6.37137187271555</v>
       </c>
       <c r="G99">
-        <v>-12.19969549418695</v>
+        <v>-8.625368975280157</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.79077484418769</v>
       </c>
       <c r="E100">
-        <v>-47.49329704084804</v>
+        <v>-47.42579787152671</v>
       </c>
       <c r="F100">
-        <v>-5.833737819827691</v>
+        <v>-6.135319883430102</v>
       </c>
       <c r="G100">
-        <v>-11.93585574981356</v>
+        <v>-9.030927960027523</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.03595605099298</v>
       </c>
       <c r="E101">
-        <v>-49.64268967961169</v>
+        <v>-51.66809496428234</v>
       </c>
       <c r="F101">
-        <v>-5.77830678670196</v>
+        <v>-5.810555129692944</v>
       </c>
       <c r="G101">
-        <v>-12.20545075680222</v>
+        <v>-9.768717190111786</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.30882243324192</v>
       </c>
       <c r="E102">
-        <v>-52.52994394835564</v>
+        <v>-52.01599950839562</v>
       </c>
       <c r="F102">
-        <v>-5.649305131063993</v>
+        <v>-6.403172483125323</v>
       </c>
       <c r="G102">
-        <v>-12.37661896067221</v>
+        <v>-10.33654570585993</v>
       </c>
     </row>
   </sheetData>
